--- a/artfynd/A 55718-2025 artfynd.xlsx
+++ b/artfynd/A 55718-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,32 +675,27 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120448306</v>
+        <v>120448273</v>
       </c>
       <c r="B2" t="n">
-        <v>57297</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>102621</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -708,29 +703,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Stormyren NV, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>446194</v>
+        <v>446289</v>
       </c>
       <c r="R2" t="n">
-        <v>6997241</v>
+        <v>6997154</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -767,7 +750,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>nyttjar bohål i tall, ca 3 m upp.</t>
+          <t>Ringhack färska till något äldre</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,6 +774,222 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>120448274</v>
+      </c>
+      <c r="B3" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Stormyren NV, Jmt</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>446287</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6997154</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Marby</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2024-10-16</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2024-10-16</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>120448306</v>
+      </c>
+      <c r="B4" t="n">
+        <v>57794</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>102621</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Sparvuggla</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Glaucidium passerinum</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Stormyren NV, Jmt</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>446194</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6997241</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Marby</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2024-10-16</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2024-10-16</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>nyttjar bohål i tall, ca 3 m upp.</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 55718-2025 artfynd.xlsx
+++ b/artfynd/A 55718-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120448273</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -876,6 +886,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120448274</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -990,8 +1005,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120448306</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>